--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="500" activeTab="10"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="账号" sheetId="1" r:id="rId1"/>
@@ -12,19 +12,20 @@
     <sheet name="用户账号" sheetId="3" r:id="rId3"/>
     <sheet name="角色" sheetId="4" r:id="rId4"/>
     <sheet name="用户角色" sheetId="5" r:id="rId5"/>
-    <sheet name="资源" sheetId="6" r:id="rId6"/>
-    <sheet name="操作" sheetId="7" r:id="rId7"/>
-    <sheet name="权限" sheetId="8" r:id="rId8"/>
-    <sheet name="角色权限" sheetId="9" r:id="rId9"/>
-    <sheet name="会话" sheetId="10" r:id="rId10"/>
-    <sheet name="日志" sheetId="11" r:id="rId11"/>
-    <sheet name="菜单" sheetId="12" r:id="rId12"/>
-    <sheet name="接口" sheetId="13" r:id="rId13"/>
-    <sheet name="页面" sheetId="14" r:id="rId14"/>
-    <sheet name="组件" sheetId="15" r:id="rId15"/>
-    <sheet name="字典类型" sheetId="16" r:id="rId16"/>
-    <sheet name="字典数据" sheetId="17" r:id="rId17"/>
-    <sheet name="系统分层" sheetId="18" r:id="rId18"/>
+    <sheet name="资源类型" sheetId="19" r:id="rId6"/>
+    <sheet name="资源" sheetId="6" r:id="rId7"/>
+    <sheet name="操作" sheetId="7" r:id="rId8"/>
+    <sheet name="权限" sheetId="8" r:id="rId9"/>
+    <sheet name="角色权限" sheetId="9" r:id="rId10"/>
+    <sheet name="会话" sheetId="10" r:id="rId11"/>
+    <sheet name="日志" sheetId="11" r:id="rId12"/>
+    <sheet name="菜单" sheetId="12" r:id="rId13"/>
+    <sheet name="接口" sheetId="13" r:id="rId14"/>
+    <sheet name="页面" sheetId="14" r:id="rId15"/>
+    <sheet name="组件" sheetId="15" r:id="rId16"/>
+    <sheet name="字典类型" sheetId="16" r:id="rId17"/>
+    <sheet name="字典数据" sheetId="17" r:id="rId18"/>
+    <sheet name="系统分层" sheetId="18" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="199">
   <si>
     <t>账号编号</t>
   </si>
@@ -175,15 +176,72 @@
     <t>名称</t>
   </si>
   <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>上级编号</t>
+  </si>
+  <si>
+    <t>前端</t>
+  </si>
+  <si>
+    <t>前端资源</t>
+  </si>
+  <si>
+    <t>后台</t>
+  </si>
+  <si>
+    <t>后端资源</t>
+  </si>
+  <si>
+    <t>页面</t>
+  </si>
+  <si>
+    <t>用户看到的页面</t>
+  </si>
+  <si>
+    <t>菜单</t>
+  </si>
+  <si>
+    <t>用户看到的菜单</t>
+  </si>
+  <si>
+    <t>目录</t>
+  </si>
+  <si>
+    <t>菜单里的目录</t>
+  </si>
+  <si>
+    <t>按钮</t>
+  </si>
+  <si>
+    <t>页面上的按钮</t>
+  </si>
+  <si>
+    <t>系统API</t>
+  </si>
+  <si>
+    <t>后台接口</t>
+  </si>
+  <si>
+    <t>数据库表</t>
+  </si>
+  <si>
+    <t>数据库列</t>
+  </si>
+  <si>
+    <t>数据库里列</t>
+  </si>
+  <si>
+    <t>数据库行</t>
+  </si>
+  <si>
+    <t>数据库里行</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>上级编号</t>
-  </si>
-  <si>
     <t>关联表</t>
   </si>
   <si>
@@ -217,25 +275,16 @@
     <t>system:system</t>
   </si>
   <si>
-    <t>菜单</t>
-  </si>
-  <si>
     <t>菜单表</t>
   </si>
   <si>
     <t>system:menu</t>
   </si>
   <si>
-    <t>按钮</t>
-  </si>
-  <si>
     <t>system:button</t>
   </si>
   <si>
     <t>系统内的所有表，数据都是资源 ，每种资源都会有唯一标识，标识符+操作符构成权限标识符，通过权限标识符，前端与后台就可以判断是否拥有某种权限</t>
-  </si>
-  <si>
-    <t>目录</t>
   </si>
   <si>
     <t>system:directory</t>
@@ -1806,60 +1855,43 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
-  <cols>
-    <col min="4" max="5" width="11.8190476190476" customWidth="1"/>
-    <col min="6" max="6" width="14.5714285714286" customWidth="1"/>
-    <col min="11" max="11" width="74.6190476190476" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="11:11">
-      <c r="K3" t="s">
-        <v>81</v>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1875,70 +1907,60 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
   <cols>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="4" max="5" width="11.8190476190476" customWidth="1"/>
+    <col min="6" max="6" width="14.5714285714286" customWidth="1"/>
+    <col min="11" max="11" width="74.6190476190476" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="F1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J3" t="s">
-        <v>95</v>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="11:11">
+      <c r="K3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1954,119 +1976,70 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
   <cols>
-    <col min="10" max="10" width="19.6571428571429" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
+      <c r="A1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1">
+        <v>104</v>
+      </c>
+      <c r="H1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1">
+      <c r="B2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>109</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J3" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2082,21 +2055,21 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5"/>
   <cols>
-    <col min="4" max="4" width="30.7428571428571" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>112</v>
@@ -2105,15 +2078,96 @@
         <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="9:9">
-      <c r="I5" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2129,43 +2183,38 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
   <cols>
-    <col min="9" max="9" width="30.5142857142857" customWidth="1"/>
+    <col min="4" max="4" width="30.7428571428571" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="9:9">
-      <c r="I3" t="s">
-        <v>118</v>
+    <row r="5" spans="9:9">
+      <c r="I5" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2181,97 +2230,42 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="7"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
   <cols>
-    <col min="12" max="12" width="32.3142857142857" customWidth="1"/>
+    <col min="9" max="9" width="30.5142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="3:5">
-      <c r="C2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="3:4">
-      <c r="C3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12">
-      <c r="C4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="3:4">
-      <c r="C5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4">
-      <c r="C6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3">
-      <c r="C7" s="1" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="3:3">
-      <c r="C8" s="1" t="s">
+    <row r="3" spans="9:9">
+      <c r="I3" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2288,42 +2282,98 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="12" max="12" width="32.3142857142857" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="3:3">
-      <c r="C2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="3:3">
-      <c r="C3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="11:11">
-      <c r="K5" t="s">
-        <v>138</v>
+    <row r="2" spans="3:5">
+      <c r="C2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4">
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12">
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="L4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4">
+      <c r="C5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4">
+      <c r="C6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2339,41 +2389,42 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D1" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="12:12">
-      <c r="L6" t="s">
-        <v>144</v>
+    <row r="2" spans="3:3">
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="11:11">
+      <c r="K5" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2389,6 +2440,56 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="12:12">
+      <c r="L6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B3:H14"/>
   <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
@@ -2400,161 +2501,161 @@
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" s="1" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="1" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="1" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="1" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="1" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="1" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2815,6 +2916,172 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="16.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="5"/>
   <cols>
@@ -2831,28 +3098,28 @@
         <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>3</v>
@@ -2863,25 +3130,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>5</v>
@@ -2892,19 +3159,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>5</v>
@@ -2915,13 +3182,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2929,10 +3196,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2940,130 +3207,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="6"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3079,13 +3226,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="3"/>
-  <cols>
-    <col min="10" max="10" width="72.1142857142857" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>66</v>
       </c>
@@ -3096,52 +3240,97 @@
         <v>68</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="10:10">
-      <c r="J4" t="s">
-        <v>71</v>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3157,43 +3346,69 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="3"/>
+  <cols>
+    <col min="10" max="10" width="72.1142857142857" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" t="s">
-        <v>72</v>
+    </row>
+    <row r="4" spans="10:10">
+      <c r="J4" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="500" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="500" firstSheet="6" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="账号" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="权限" sheetId="8" r:id="rId9"/>
     <sheet name="角色权限" sheetId="9" r:id="rId10"/>
     <sheet name="会话" sheetId="10" r:id="rId11"/>
-    <sheet name="日志" sheetId="11" r:id="rId12"/>
-    <sheet name="菜单" sheetId="12" r:id="rId13"/>
-    <sheet name="接口" sheetId="13" r:id="rId14"/>
-    <sheet name="页面" sheetId="14" r:id="rId15"/>
-    <sheet name="组件" sheetId="15" r:id="rId16"/>
-    <sheet name="字典类型" sheetId="16" r:id="rId17"/>
-    <sheet name="字典数据" sheetId="17" r:id="rId18"/>
-    <sheet name="系统分层" sheetId="18" r:id="rId19"/>
+    <sheet name="系统操作日志" sheetId="11" r:id="rId12"/>
+    <sheet name="三方接口日志" sheetId="20" r:id="rId13"/>
+    <sheet name="菜单" sheetId="12" r:id="rId14"/>
+    <sheet name="接口" sheetId="13" r:id="rId15"/>
+    <sheet name="页面" sheetId="14" r:id="rId16"/>
+    <sheet name="组件" sheetId="15" r:id="rId17"/>
+    <sheet name="字典类型" sheetId="16" r:id="rId18"/>
+    <sheet name="字典数据" sheetId="17" r:id="rId19"/>
+    <sheet name="系统分层" sheetId="18" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="204">
   <si>
     <t>账号编号</t>
   </si>
@@ -449,6 +450,21 @@
   </si>
   <si>
     <t>系统中所有操作都会被记录日志，且日志不能进行修改，删除操作，只能进行查询操作</t>
+  </si>
+  <si>
+    <t>请求方式</t>
+  </si>
+  <si>
+    <t>请求路径</t>
+  </si>
+  <si>
+    <t>请求参数</t>
+  </si>
+  <si>
+    <t>响应参数</t>
+  </si>
+  <si>
+    <t>耗时</t>
   </si>
   <si>
     <t>图标</t>
@@ -2055,6 +2071,48 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="4" width="13.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="16.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5"/>
   <cols>
@@ -2072,16 +2130,16 @@
         <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -2092,7 +2150,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2100,7 +2158,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2108,10 +2166,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2119,7 +2177,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2127,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2135,7 +2193,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2143,7 +2201,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2151,7 +2209,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2159,7 +2217,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2167,54 +2225,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
-  <cols>
-    <col min="4" max="4" width="30.7428571428571" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="9:9">
-      <c r="I5" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2230,43 +2241,38 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
   <cols>
-    <col min="9" max="9" width="30.5142857142857" customWidth="1"/>
+    <col min="4" max="4" width="30.7428571428571" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="9:9">
-      <c r="I3" t="s">
-        <v>134</v>
+    <row r="5" spans="9:9">
+      <c r="I5" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2282,98 +2288,43 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="7"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="2"/>
   <cols>
-    <col min="12" max="12" width="32.3142857142857" customWidth="1"/>
+    <col min="9" max="9" width="30.5142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="3" spans="9:9">
+      <c r="I3" t="s">
         <v>139</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="3:5">
-      <c r="C2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="3:4">
-      <c r="C3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12">
-      <c r="C4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="L4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="3:4">
-      <c r="C5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4">
-      <c r="C6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3">
-      <c r="C7" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3">
-      <c r="C8" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2389,42 +2340,98 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="12" max="12" width="32.3142857142857" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="3:5">
+      <c r="C2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4">
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12">
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4">
+      <c r="C5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="3:3">
-      <c r="C2" t="s">
+      <c r="D5" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
-      <c r="C3" t="s">
+    <row r="6" spans="3:4">
+      <c r="C6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="11:11">
-      <c r="K5" t="s">
+    <row r="7" spans="3:3">
+      <c r="C7" s="1" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2440,41 +2447,42 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="4"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
         <v>156</v>
       </c>
       <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="3:3">
+      <c r="C2" t="s">
         <v>157</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
         <v>158</v>
       </c>
-      <c r="F1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="5" spans="11:11">
+      <c r="K5" t="s">
         <v>159</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="12:12">
-      <c r="L6" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2490,172 +2498,41 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:H14"/>
-  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelCol="7"/>
-  <cols>
-    <col min="3" max="3" width="19.4761904761905" style="1" customWidth="1"/>
-    <col min="4" max="4" width="116.847619047619" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.2095238095238" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.0190476190476" style="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelRow="5"/>
   <sheetData>
-    <row r="3" spans="2:8">
-      <c r="B3" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D1" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E1" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="12:12">
+      <c r="L6" t="s">
         <v>165</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2726,6 +2603,187 @@
       </c>
       <c r="H4" t="s">
         <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B3:H14"/>
+  <sheetFormatPr defaultColWidth="11.5333333333333" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <cols>
+    <col min="3" max="3" width="19.4761904761905" style="1" customWidth="1"/>
+    <col min="4" max="4" width="116.847619047619" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.2095238095238" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.0190476190476" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8">
+      <c r="B3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
